--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_backtest_metrics.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.9770769857351751</v>
+        <v>1.200265980992737</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>-0.02292301426482168</v>
+        <v>0.2002659809927303</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-0.004384224003176951</v>
+        <v>0.03519222014663193</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.01266081831727273</v>
+        <v>0.05291481517535668</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.2634352225510318</v>
+        <v>0.2007489212042406</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.05863405292118513</v>
+        <v>0.1981773408586734</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.08331115331074841</v>
+        <v>0.2896193115846567</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.4730137796046834</v>
+        <v>0.3589825350599136</v>
       </c>
     </row>
     <row r="14">
@@ -699,7 +699,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2025年06月</t>
+          <t>2021年09月-2024年09月</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.009268702503426058</v>
+        <v>0.09803323758009118</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2187952444856272</v>
+        <v>0.1577492509143567</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.132535774944869</v>
+        <v>0.3381049962338869</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.3741118104502492</v>
+        <v>0.1991001465652867</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2024年02月-2025年07月</t>
+          <t>2024年02月-2025年12月</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>25.81732363781598</v>
+        <v>19.26171408845711</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.1029917588642193</v>
+        <v>0.07683979333179741</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.2393186522800572</v>
+        <v>0.184615373407111</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>2.602255639097744</v>
+        <v>8.635338345864662</v>
       </c>
     </row>
     <row r="24">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/close/close_backtest_metrics.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1.200265980992737</v>
+        <v>0.7637979707726115</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.2002659809927303</v>
+        <v>-0.2362020292273824</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.03519222014663193</v>
+        <v>-0.04977269611334934</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.05291481517535668</v>
+        <v>-0.03350470900499147</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.2007489212042406</v>
+        <v>0.2109870243177223</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1981773408586734</v>
+        <v>-0.2070322653104334</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2896193115846567</v>
+        <v>-0.2900988374837543</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.3589825350599136</v>
+        <v>0.4727931365748604</v>
       </c>
     </row>
     <row r="14">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.09803323758009118</v>
+        <v>-0.1052737281127356</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.1577492509143567</v>
+        <v>0.1854943146707613</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3381049962338869</v>
+        <v>-0.1624265366153639</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.1991001465652867</v>
+        <v>0.3887694423527188</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2024年02月-2025年12月</t>
+          <t>2024年02月-2026年06月</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>19.26171408845711</v>
+        <v>19.12285270920735</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.07683979333179741</v>
+        <v>0.07628584057170991</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.184615373407111</v>
+        <v>0.1836095665030772</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>8.635338345864662</v>
+        <v>3.221804511278195</v>
       </c>
     </row>
     <row r="24">
